--- a/backend/data/financials_by_company/000875.SZ.xlsx
+++ b/backend/data/financials_by_company/000875.SZ.xlsx
@@ -697,656 +697,656 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-26778564.194142</v>
+        <v>-11498700.410029</v>
       </c>
       <c r="C2" t="n">
-        <v>0.155652</v>
+        <v>0.181292</v>
       </c>
       <c r="D2" t="n">
-        <v>7484555558.77</v>
+        <v>5598588865.08</v>
       </c>
       <c r="E2" t="n">
-        <v>-172040861.52</v>
+        <v>-63426491.54</v>
       </c>
       <c r="F2" t="n">
-        <v>-172040861.52</v>
+        <v>-63426491.54</v>
       </c>
       <c r="G2" t="n">
-        <v>1099239157.13</v>
+        <v>500043875.15</v>
       </c>
       <c r="H2" t="n">
-        <v>3860070719.05</v>
+        <v>2830698657.45</v>
       </c>
       <c r="I2" t="n">
-        <v>10040988908.24</v>
+        <v>10374613378.88</v>
       </c>
       <c r="J2" t="n">
-        <v>7312514697.25</v>
+        <v>5535162373.54</v>
       </c>
       <c r="K2" t="n">
-        <v>3452443978.2</v>
+        <v>2704463716.09</v>
       </c>
       <c r="L2" t="n">
-        <v>-1446843522.72</v>
+        <v>-1684684011.65</v>
       </c>
       <c r="M2" t="n">
-        <v>1454381926.24</v>
+        <v>1655647204.62</v>
       </c>
       <c r="N2" t="n">
-        <v>10396320.67</v>
+        <v>11267994.66</v>
       </c>
       <c r="O2" t="n">
-        <v>1244501454.455858</v>
+        <v>551971666.279971</v>
       </c>
       <c r="P2" t="n">
-        <v>1099239157.13</v>
+        <v>500043875.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>10328002707.82</v>
+        <v>10575586069.74</v>
       </c>
       <c r="R2" t="n">
-        <v>10388340.06</v>
+        <v>837507.29</v>
       </c>
       <c r="S2" t="n">
-        <v>1820479562.25</v>
+        <v>978869097.6900001</v>
       </c>
       <c r="T2" t="n">
-        <v>2892734624</v>
+        <v>2631809869</v>
       </c>
       <c r="U2" t="n">
-        <v>2892734624</v>
+        <v>2631809869</v>
       </c>
       <c r="V2" t="n">
-        <v>0.38</v>
+        <v>0.19</v>
       </c>
       <c r="W2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
+        <v>0.19</v>
+      </c>
+      <c r="X2" t="n">
+        <v>500043875.15</v>
+      </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1099239157.13</v>
+        <v>500043875.15</v>
       </c>
       <c r="AA2" t="n">
-        <v>-587819843.29</v>
+        <v>-358630842.92</v>
       </c>
       <c r="AB2" t="n">
-        <v>1687059000.42</v>
+        <v>858674718.0700001</v>
       </c>
       <c r="AC2" t="n">
-        <v>1687059000.42</v>
+        <v>858674718.0700001</v>
       </c>
       <c r="AD2" t="n">
-        <v>311003051.54</v>
+        <v>190141793.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>1998062051.96</v>
+        <v>1048816511.47</v>
       </c>
       <c r="AF2" t="n">
-        <v>177582489.71</v>
+        <v>69947413.78</v>
       </c>
       <c r="AG2" t="n">
-        <v>-172040861.52</v>
+        <v>-36994924.37</v>
       </c>
       <c r="AH2" t="n">
-        <v>-7263744</v>
+        <v>-13183209.51</v>
       </c>
       <c r="AI2" t="n">
-        <v>68465428</v>
+        <v>12982033.88</v>
       </c>
       <c r="AJ2" t="n">
-        <v>110839177.52</v>
+        <v>37196100</v>
       </c>
       <c r="AK2" t="n">
-        <v>-1446843522.72</v>
+        <v>-1684684011.65</v>
       </c>
       <c r="AL2" t="n">
-        <v>2857917.15</v>
+        <v>40304801.69</v>
       </c>
       <c r="AM2" t="n">
-        <v>1454381926.24</v>
+        <v>1655647204.62</v>
       </c>
       <c r="AN2" t="n">
-        <v>10396320.67</v>
+        <v>11267994.66</v>
       </c>
       <c r="AO2" t="n">
-        <v>3411736707.16</v>
+        <v>2678218092.05</v>
       </c>
       <c r="AP2" t="n">
-        <v>287013799.58</v>
+        <v>200972690.86</v>
       </c>
       <c r="AQ2" t="n">
-        <v>119794623.83</v>
+        <v>108051857.88</v>
       </c>
       <c r="AR2" t="n">
-        <v>13611346.07</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+        <v>9307464.08</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1876706.46</v>
+      </c>
       <c r="AT2" t="n">
-        <v>13611346.07</v>
+        <v>7430757.62</v>
       </c>
       <c r="AU2" t="n">
-        <v>63710457.48</v>
+        <v>57124830.9</v>
       </c>
       <c r="AV2" t="n">
-        <v>54571870.11</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
+        <v>48305894.89</v>
+      </c>
+      <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="n">
-        <v>54571870.11</v>
+        <v>48305894.89</v>
       </c>
       <c r="AY2" t="n">
-        <v>10388340.06</v>
+        <v>837507.29</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3698750506.74</v>
+        <v>2879190782.91</v>
       </c>
       <c r="BA2" t="n">
-        <v>10040988908.24</v>
+        <v>10374613378.88</v>
       </c>
       <c r="BB2" t="n">
-        <v>13739739414.98</v>
+        <v>13253804161.79</v>
       </c>
       <c r="BC2" t="n">
-        <v>13739739414.98</v>
+        <v>13253804161.79</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-22219101.202191</v>
+        <v>-18154693.10925</v>
       </c>
       <c r="C3" t="n">
-        <v>0.176463</v>
+        <v>0.168467</v>
       </c>
       <c r="D3" t="n">
-        <v>7046977408.23</v>
+        <v>6710811751.85</v>
       </c>
       <c r="E3" t="n">
-        <v>-125913559.42</v>
+        <v>-107764343.77</v>
       </c>
       <c r="F3" t="n">
-        <v>-125913559.42</v>
+        <v>-107764343.77</v>
       </c>
       <c r="G3" t="n">
-        <v>908417734.74</v>
+        <v>674617035.72</v>
       </c>
       <c r="H3" t="n">
-        <v>3528599463.68</v>
+        <v>3339810397.12</v>
       </c>
       <c r="I3" t="n">
-        <v>10723436552.19</v>
+        <v>11377576252.91</v>
       </c>
       <c r="J3" t="n">
-        <v>6921063848.81</v>
+        <v>6603047408.08</v>
       </c>
       <c r="K3" t="n">
-        <v>3392464385.13</v>
+        <v>3263237010.96</v>
       </c>
       <c r="L3" t="n">
-        <v>-1482415619.36</v>
+        <v>-1833652586.76</v>
       </c>
       <c r="M3" t="n">
-        <v>1494357544.24</v>
+        <v>1839707230.8</v>
       </c>
       <c r="N3" t="n">
-        <v>13910259.93</v>
+        <v>18448048</v>
       </c>
       <c r="O3" t="n">
-        <v>1012112192.957809</v>
+        <v>764226686.3807499</v>
       </c>
       <c r="P3" t="n">
-        <v>908417734.74</v>
+        <v>674617035.72</v>
       </c>
       <c r="Q3" t="n">
-        <v>11041661478.19</v>
+        <v>11641828467.55</v>
       </c>
       <c r="R3" t="n">
-        <v>12531560.69</v>
+        <v>10517633.15</v>
       </c>
       <c r="S3" t="n">
-        <v>1858300481.26</v>
+        <v>1454242775.9</v>
       </c>
       <c r="T3" t="n">
-        <v>2752781014</v>
+        <v>2810904316</v>
       </c>
       <c r="U3" t="n">
-        <v>2752781014</v>
+        <v>2810904316</v>
       </c>
       <c r="V3" t="n">
-        <v>0.33</v>
+        <v>0.24</v>
       </c>
       <c r="W3" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="X3" t="inlineStr"/>
+        <v>0.24</v>
+      </c>
+      <c r="X3" t="n">
+        <v>674617035.72</v>
+      </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>908417734.74</v>
+        <v>674617035.72</v>
       </c>
       <c r="AA3" t="n">
-        <v>-654743225.9400001</v>
+        <v>-509095515.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>1563160960.68</v>
+        <v>1183712551.32</v>
       </c>
       <c r="AC3" t="n">
-        <v>1563160960.68</v>
+        <v>1183712551.32</v>
       </c>
       <c r="AD3" t="n">
-        <v>334945880.21</v>
+        <v>239817228.84</v>
       </c>
       <c r="AE3" t="n">
-        <v>1898106840.89</v>
+        <v>1423529780.16</v>
       </c>
       <c r="AF3" t="n">
-        <v>39806359.63</v>
+        <v>-30712995.74</v>
       </c>
       <c r="AG3" t="n">
-        <v>-125913559.42</v>
+        <v>-107764343.77</v>
       </c>
       <c r="AH3" t="n">
-        <v>6443568.26</v>
+        <v>14830.06</v>
       </c>
       <c r="AI3" t="n">
-        <v>114452104.15</v>
+        <v>57010879.2</v>
       </c>
       <c r="AJ3" t="n">
-        <v>5017887.01</v>
+        <v>50738634.51</v>
       </c>
       <c r="AK3" t="n">
-        <v>-1482415619.36</v>
+        <v>-1833652586.76</v>
       </c>
       <c r="AL3" t="n">
-        <v>1968335.05</v>
+        <v>12393403.96</v>
       </c>
       <c r="AM3" t="n">
-        <v>1494357544.24</v>
+        <v>1839707230.8</v>
       </c>
       <c r="AN3" t="n">
-        <v>13910259.93</v>
+        <v>18448048</v>
       </c>
       <c r="AO3" t="n">
-        <v>3400938249.21</v>
+        <v>3312925257.57</v>
       </c>
       <c r="AP3" t="n">
-        <v>318224926</v>
+        <v>264252214.64</v>
       </c>
       <c r="AQ3" t="n">
-        <v>122745192.61</v>
+        <v>115509822.94</v>
       </c>
       <c r="AR3" t="n">
-        <v>14600282.6</v>
+        <v>12004563.88</v>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
-        <v>14600282.6</v>
+        <v>12004563.88</v>
       </c>
       <c r="AU3" t="n">
-        <v>78760068.59</v>
+        <v>62081211.18</v>
       </c>
       <c r="AV3" t="n">
-        <v>60338236.67</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
+        <v>50894962.61</v>
+      </c>
+      <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="n">
-        <v>60338236.67</v>
+        <v>50894962.61</v>
       </c>
       <c r="AY3" t="n">
-        <v>12531560.69</v>
+        <v>10517633.15</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3719163175.21</v>
+        <v>3577177472.21</v>
       </c>
       <c r="BA3" t="n">
-        <v>10723436552.19</v>
+        <v>11377576252.91</v>
       </c>
       <c r="BB3" t="n">
-        <v>14442599727.4</v>
+        <v>14954753725.12</v>
       </c>
       <c r="BC3" t="n">
-        <v>14442599727.4</v>
+        <v>14954753725.12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-18154693.10925</v>
+        <v>-22219101.202191</v>
       </c>
       <c r="C4" t="n">
-        <v>0.168467</v>
+        <v>0.176463</v>
       </c>
       <c r="D4" t="n">
-        <v>6710811751.85</v>
+        <v>7046977408.23</v>
       </c>
       <c r="E4" t="n">
-        <v>-107764343.77</v>
+        <v>-125913559.42</v>
       </c>
       <c r="F4" t="n">
-        <v>-107764343.77</v>
+        <v>-125913559.42</v>
       </c>
       <c r="G4" t="n">
-        <v>674617035.72</v>
+        <v>908417734.74</v>
       </c>
       <c r="H4" t="n">
-        <v>3339810397.12</v>
+        <v>3528599463.68</v>
       </c>
       <c r="I4" t="n">
-        <v>11377576252.91</v>
+        <v>10723436552.19</v>
       </c>
       <c r="J4" t="n">
-        <v>6603047408.08</v>
+        <v>6921063848.81</v>
       </c>
       <c r="K4" t="n">
-        <v>3263237010.96</v>
+        <v>3392464385.13</v>
       </c>
       <c r="L4" t="n">
-        <v>-1833652586.76</v>
+        <v>-1482415619.36</v>
       </c>
       <c r="M4" t="n">
-        <v>1839707230.8</v>
+        <v>1494357544.24</v>
       </c>
       <c r="N4" t="n">
-        <v>18448048</v>
+        <v>13910259.93</v>
       </c>
       <c r="O4" t="n">
-        <v>764226686.3807499</v>
+        <v>1012112192.957809</v>
       </c>
       <c r="P4" t="n">
-        <v>674617035.72</v>
+        <v>908417734.74</v>
       </c>
       <c r="Q4" t="n">
-        <v>11641828467.55</v>
+        <v>11041661478.19</v>
       </c>
       <c r="R4" t="n">
-        <v>10517633.15</v>
+        <v>12531560.69</v>
       </c>
       <c r="S4" t="n">
-        <v>1454242775.9</v>
+        <v>1858300481.26</v>
       </c>
       <c r="T4" t="n">
-        <v>2810904316</v>
+        <v>2752781014</v>
       </c>
       <c r="U4" t="n">
-        <v>2810904316</v>
+        <v>2752781014</v>
       </c>
       <c r="V4" t="n">
-        <v>0.24</v>
+        <v>0.33</v>
       </c>
       <c r="W4" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="X4" t="n">
-        <v>674617035.72</v>
-      </c>
+        <v>0.33</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>674617035.72</v>
+        <v>908417734.74</v>
       </c>
       <c r="AA4" t="n">
-        <v>-509095515.6</v>
+        <v>-654743225.9400001</v>
       </c>
       <c r="AB4" t="n">
-        <v>1183712551.32</v>
+        <v>1563160960.68</v>
       </c>
       <c r="AC4" t="n">
-        <v>1183712551.32</v>
+        <v>1563160960.68</v>
       </c>
       <c r="AD4" t="n">
-        <v>239817228.84</v>
+        <v>334945880.21</v>
       </c>
       <c r="AE4" t="n">
-        <v>1423529780.16</v>
+        <v>1898106840.89</v>
       </c>
       <c r="AF4" t="n">
-        <v>-30712995.74</v>
+        <v>39806359.63</v>
       </c>
       <c r="AG4" t="n">
-        <v>-107764343.77</v>
+        <v>-125913559.42</v>
       </c>
       <c r="AH4" t="n">
-        <v>14830.06</v>
+        <v>6443568.26</v>
       </c>
       <c r="AI4" t="n">
-        <v>57010879.2</v>
+        <v>114452104.15</v>
       </c>
       <c r="AJ4" t="n">
-        <v>50738634.51</v>
+        <v>5017887.01</v>
       </c>
       <c r="AK4" t="n">
-        <v>-1833652586.76</v>
+        <v>-1482415619.36</v>
       </c>
       <c r="AL4" t="n">
-        <v>12393403.96</v>
+        <v>1968335.05</v>
       </c>
       <c r="AM4" t="n">
-        <v>1839707230.8</v>
+        <v>1494357544.24</v>
       </c>
       <c r="AN4" t="n">
-        <v>18448048</v>
+        <v>13910259.93</v>
       </c>
       <c r="AO4" t="n">
-        <v>3312925257.57</v>
+        <v>3400938249.21</v>
       </c>
       <c r="AP4" t="n">
-        <v>264252214.64</v>
+        <v>318224926</v>
       </c>
       <c r="AQ4" t="n">
-        <v>115509822.94</v>
+        <v>122745192.61</v>
       </c>
       <c r="AR4" t="n">
-        <v>12004563.88</v>
+        <v>14600282.6</v>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>12004563.88</v>
+        <v>14600282.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>62081211.18</v>
+        <v>78760068.59</v>
       </c>
       <c r="AV4" t="n">
-        <v>50894962.61</v>
-      </c>
-      <c r="AW4" t="inlineStr"/>
+        <v>60338236.67</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
       <c r="AX4" t="n">
-        <v>50894962.61</v>
+        <v>60338236.67</v>
       </c>
       <c r="AY4" t="n">
-        <v>10517633.15</v>
+        <v>12531560.69</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3577177472.21</v>
+        <v>3719163175.21</v>
       </c>
       <c r="BA4" t="n">
-        <v>11377576252.91</v>
+        <v>10723436552.19</v>
       </c>
       <c r="BB4" t="n">
-        <v>14954753725.12</v>
+        <v>14442599727.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>14954753725.12</v>
+        <v>14442599727.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-11498700.410029</v>
+        <v>-26778564.194142</v>
       </c>
       <c r="C5" t="n">
-        <v>0.181292</v>
+        <v>0.155652</v>
       </c>
       <c r="D5" t="n">
-        <v>5598588865.08</v>
+        <v>7484555558.77</v>
       </c>
       <c r="E5" t="n">
-        <v>-63426491.54</v>
+        <v>-172040861.52</v>
       </c>
       <c r="F5" t="n">
-        <v>-63426491.54</v>
+        <v>-172040861.52</v>
       </c>
       <c r="G5" t="n">
-        <v>500043875.15</v>
+        <v>1099239157.13</v>
       </c>
       <c r="H5" t="n">
-        <v>2830698657.45</v>
+        <v>3860070719.05</v>
       </c>
       <c r="I5" t="n">
-        <v>10374613378.88</v>
+        <v>10040988908.24</v>
       </c>
       <c r="J5" t="n">
-        <v>5535162373.54</v>
+        <v>7312514697.25</v>
       </c>
       <c r="K5" t="n">
-        <v>2704463716.09</v>
+        <v>3452443978.2</v>
       </c>
       <c r="L5" t="n">
-        <v>-1684684011.65</v>
+        <v>-1446843522.72</v>
       </c>
       <c r="M5" t="n">
-        <v>1655647204.62</v>
+        <v>1454381926.24</v>
       </c>
       <c r="N5" t="n">
-        <v>11267994.66</v>
+        <v>10396320.67</v>
       </c>
       <c r="O5" t="n">
-        <v>551971666.279971</v>
+        <v>1244501454.455858</v>
       </c>
       <c r="P5" t="n">
-        <v>500043875.15</v>
+        <v>1099239157.13</v>
       </c>
       <c r="Q5" t="n">
-        <v>10575586069.74</v>
+        <v>10328002707.82</v>
       </c>
       <c r="R5" t="n">
-        <v>837507.29</v>
+        <v>10388340.06</v>
       </c>
       <c r="S5" t="n">
-        <v>978869097.6900001</v>
+        <v>1820479562.25</v>
       </c>
       <c r="T5" t="n">
-        <v>2631809869</v>
+        <v>2892734624</v>
       </c>
       <c r="U5" t="n">
-        <v>2631809869</v>
+        <v>2892734624</v>
       </c>
       <c r="V5" t="n">
-        <v>0.19</v>
+        <v>0.38</v>
       </c>
       <c r="W5" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="X5" t="n">
-        <v>500043875.15</v>
-      </c>
+        <v>0.38</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>500043875.15</v>
+        <v>1099239157.13</v>
       </c>
       <c r="AA5" t="n">
-        <v>-358630842.92</v>
+        <v>-587819843.29</v>
       </c>
       <c r="AB5" t="n">
-        <v>858674718.0700001</v>
+        <v>1687059000.42</v>
       </c>
       <c r="AC5" t="n">
-        <v>858674718.0700001</v>
+        <v>1687059000.42</v>
       </c>
       <c r="AD5" t="n">
-        <v>190141793.4</v>
+        <v>311003051.54</v>
       </c>
       <c r="AE5" t="n">
-        <v>1048816511.47</v>
+        <v>1998062051.96</v>
       </c>
       <c r="AF5" t="n">
-        <v>69947413.78</v>
+        <v>177582489.71</v>
       </c>
       <c r="AG5" t="n">
-        <v>-36994924.37</v>
+        <v>-172040861.52</v>
       </c>
       <c r="AH5" t="n">
-        <v>-13183209.51</v>
+        <v>-7263744</v>
       </c>
       <c r="AI5" t="n">
-        <v>12982033.88</v>
+        <v>68465428</v>
       </c>
       <c r="AJ5" t="n">
-        <v>37196100</v>
+        <v>110839177.52</v>
       </c>
       <c r="AK5" t="n">
-        <v>-1684684011.65</v>
+        <v>-1446843522.72</v>
       </c>
       <c r="AL5" t="n">
-        <v>40304801.69</v>
+        <v>2857917.15</v>
       </c>
       <c r="AM5" t="n">
-        <v>1655647204.62</v>
+        <v>1454381926.24</v>
       </c>
       <c r="AN5" t="n">
-        <v>11267994.66</v>
+        <v>10396320.67</v>
       </c>
       <c r="AO5" t="n">
-        <v>2678218092.05</v>
+        <v>3411736707.16</v>
       </c>
       <c r="AP5" t="n">
-        <v>200972690.86</v>
+        <v>287013799.58</v>
       </c>
       <c r="AQ5" t="n">
-        <v>108051857.88</v>
+        <v>119794623.83</v>
       </c>
       <c r="AR5" t="n">
-        <v>9307464.08</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1876706.46</v>
-      </c>
+        <v>13611346.07</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>7430757.62</v>
+        <v>13611346.07</v>
       </c>
       <c r="AU5" t="n">
-        <v>57124830.9</v>
+        <v>63710457.48</v>
       </c>
       <c r="AV5" t="n">
-        <v>48305894.89</v>
-      </c>
-      <c r="AW5" t="inlineStr"/>
+        <v>54571870.11</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
       <c r="AX5" t="n">
-        <v>48305894.89</v>
+        <v>54571870.11</v>
       </c>
       <c r="AY5" t="n">
-        <v>837507.29</v>
+        <v>10388340.06</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2879190782.91</v>
+        <v>3698750506.74</v>
       </c>
       <c r="BA5" t="n">
-        <v>10374613378.88</v>
+        <v>10040988908.24</v>
       </c>
       <c r="BB5" t="n">
-        <v>13253804161.79</v>
+        <v>13739739414.98</v>
       </c>
       <c r="BC5" t="n">
-        <v>13253804161.79</v>
+        <v>13739739414.98</v>
       </c>
     </row>
   </sheetData>
@@ -1747,236 +1747,224 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>3627270626</v>
+        <v>2790208174</v>
       </c>
       <c r="C2" t="n">
-        <v>3627270626</v>
+        <v>2790208174</v>
       </c>
       <c r="D2" t="n">
-        <v>36149213931.89</v>
+        <v>35916222552.6</v>
       </c>
       <c r="E2" t="n">
-        <v>49606474965.75</v>
+        <v>40752715786.25</v>
       </c>
       <c r="F2" t="n">
-        <v>14908207053.77</v>
+        <v>9597008989.98</v>
       </c>
       <c r="G2" t="n">
-        <v>53766121201.29</v>
+        <v>47354072702.47</v>
       </c>
       <c r="H2" t="n">
-        <v>-10726920109.76</v>
+        <v>-9479411357.969999</v>
       </c>
       <c r="I2" t="n">
-        <v>14908207053.77</v>
+        <v>9597008989.98</v>
       </c>
       <c r="J2" t="n">
-        <v>1161418979.06</v>
+        <v>692135458.46</v>
       </c>
       <c r="K2" t="n">
-        <v>16757287629.58</v>
+        <v>10506014995.17</v>
       </c>
       <c r="L2" t="n">
-        <v>47545721368.29</v>
+        <v>36816354641.09</v>
       </c>
       <c r="M2" t="n">
-        <v>24899870613.77</v>
+        <v>14353561483.5</v>
       </c>
       <c r="N2" t="n">
-        <v>8142582984.19</v>
+        <v>3847546488.33</v>
       </c>
       <c r="O2" t="n">
-        <v>16757287629.58</v>
+        <v>10506014995.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2539210152.78</v>
+        <v>563525276.85</v>
       </c>
       <c r="Q2" t="n">
-        <v>9349565210.540001</v>
+        <v>6017730560.46</v>
       </c>
       <c r="R2" t="n">
-        <v>3627270626</v>
+        <v>2790208174</v>
       </c>
       <c r="S2" t="n">
-        <v>3627270626</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
+        <v>2790208174</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>58063902576.59</v>
+        <v>52471737956.36</v>
       </c>
       <c r="V2" t="n">
-        <v>34732184834.21</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
+        <v>31048997489.06</v>
+      </c>
+      <c r="W2" t="n">
+        <v>3803400535.26</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
-        <v>2537752669.87</v>
+        <v>3810558289.06</v>
       </c>
       <c r="Z2" t="n">
-        <v>118582311.06</v>
+        <v>68756218.73999999</v>
       </c>
       <c r="AA2" t="n">
-        <v>125997135.51</v>
+        <v>167207876.88</v>
       </c>
       <c r="AB2" t="n">
-        <v>31949852717.77</v>
+        <v>27002475104.38</v>
       </c>
       <c r="AC2" t="n">
-        <v>1161418979.06</v>
+        <v>692135458.46</v>
       </c>
       <c r="AD2" t="n">
-        <v>30788433738.71</v>
+        <v>26310339645.92</v>
       </c>
       <c r="AE2" t="n">
-        <v>23331717742.38</v>
+        <v>21422740467.3</v>
       </c>
       <c r="AF2" t="n">
-        <v>647545583.63</v>
+        <v>3058384259.31</v>
       </c>
       <c r="AG2" t="n">
-        <v>17656622247.98</v>
+        <v>13750240681.87</v>
       </c>
       <c r="AH2" t="n">
-        <v>6220399833</v>
+        <v>10537718061.38</v>
       </c>
       <c r="AI2" t="n">
-        <v>4603158100.31</v>
+        <v>4252389016.34</v>
       </c>
       <c r="AJ2" t="n">
-        <v>865819195.53</v>
+        <v>822903238.91</v>
       </c>
       <c r="AK2" t="n">
-        <v>40206489.88</v>
+        <v>137678575.79</v>
       </c>
       <c r="AL2" t="n">
-        <v>173252662.91</v>
+        <v>162204778.06</v>
       </c>
       <c r="AM2" t="n">
-        <v>3523879751.99</v>
+        <v>3129602423.58</v>
       </c>
       <c r="AN2" t="n">
-        <v>82963773190.36</v>
+        <v>66825299439.86</v>
       </c>
       <c r="AO2" t="n">
-        <v>70358975557.74001</v>
+        <v>54881970330.53</v>
       </c>
       <c r="AP2" t="n">
-        <v>3275452363.01</v>
+        <v>1526367011.27</v>
       </c>
       <c r="AQ2" t="n">
-        <v>394538026.16</v>
+        <v>13156353.18</v>
       </c>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
-        <v>335651617.88</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
+        <v>208447230.71</v>
+      </c>
+      <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="n">
-        <v>335651617.88</v>
+        <v>208447230.71</v>
       </c>
       <c r="AV2" t="n">
-        <v>1220158426.68</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
+        <v>634098603.72</v>
+      </c>
+      <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="n">
-        <v>1849080575.81</v>
+        <v>909006005.1900001</v>
       </c>
       <c r="AY2" t="n">
-        <v>1844458923.53</v>
+        <v>854614286.23</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4621652.28</v>
+        <v>54391718.96</v>
       </c>
       <c r="BA2" t="n">
-        <v>63039997301.4</v>
+        <v>51374407101.26</v>
       </c>
       <c r="BB2" t="n">
-        <v>-28359527107.42</v>
+        <v>-18148593744.7</v>
       </c>
       <c r="BC2" t="n">
-        <v>91399524408.82001</v>
+        <v>69523000845.96001</v>
       </c>
       <c r="BD2" t="n">
-        <v>7336977099.32</v>
+        <v>5906608730.28</v>
       </c>
       <c r="BE2" t="n">
-        <v>1917160993.08</v>
+        <v>1603881533.92</v>
       </c>
       <c r="BF2" t="n">
-        <v>73105399280.73</v>
+        <v>54675512670.24</v>
       </c>
       <c r="BG2" t="n">
-        <v>9039987035.690001</v>
+        <v>7336997911.52</v>
       </c>
       <c r="BH2" t="n">
-        <v>12604797632.62</v>
+        <v>11943329109.33</v>
       </c>
       <c r="BI2" t="n">
-        <v>653199955.25</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0</v>
-      </c>
+        <v>965594662.83</v>
+      </c>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
       <c r="BL2" t="n">
-        <v>230688825.24</v>
+        <v>942834940.1900001</v>
       </c>
       <c r="BM2" t="n">
-        <v>305356902.25</v>
+        <v>411176363.58</v>
       </c>
       <c r="BN2" t="n">
         <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>13255197.78</v>
+        <v>6222614.11</v>
       </c>
       <c r="BP2" t="n">
-        <v>292101704.47</v>
+        <v>404953749.47</v>
       </c>
       <c r="BQ2" t="n">
-        <v>378576738.21</v>
+        <v>337772104.34</v>
       </c>
       <c r="BR2" t="n">
-        <v>10176355571.85</v>
+        <v>8354115883.69</v>
       </c>
       <c r="BS2" t="n">
-        <v>-215666184.85</v>
+        <v>-38890442.3</v>
       </c>
       <c r="BT2" t="n">
-        <v>10392021756.7</v>
+        <v>8393006325.99</v>
       </c>
       <c r="BU2" t="n">
-        <v>860619639.8200001</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>1000000</v>
-      </c>
+        <v>931835154.7</v>
+      </c>
+      <c r="BV2" t="inlineStr"/>
       <c r="BW2" t="n">
-        <v>859619639.8200001</v>
+        <v>931835154.7</v>
       </c>
       <c r="BX2" t="n">
-        <v>45055290</v>
+        <v>55026279.87</v>
       </c>
       <c r="BY2" t="n">
-        <v>814564349.8200001</v>
+        <v>876808874.83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>2790208174</v>
@@ -1985,43 +1973,43 @@
         <v>2790208174</v>
       </c>
       <c r="D3" t="n">
-        <v>41734015873.84</v>
+        <v>36631305188.61</v>
       </c>
       <c r="E3" t="n">
-        <v>49198993015.08</v>
+        <v>43901121837.24</v>
       </c>
       <c r="F3" t="n">
-        <v>10051519742.54</v>
+        <v>10232272325.44</v>
       </c>
       <c r="G3" t="n">
-        <v>54632025807.73</v>
+        <v>49157790586.21</v>
       </c>
       <c r="H3" t="n">
-        <v>-6424865354.74</v>
+        <v>-5573426743.96</v>
       </c>
       <c r="I3" t="n">
-        <v>10051519742.54</v>
+        <v>10232272325.44</v>
       </c>
       <c r="J3" t="n">
-        <v>969372890.45</v>
+        <v>728331018.25</v>
       </c>
       <c r="K3" t="n">
-        <v>11798504627</v>
+        <v>11178100067.21</v>
       </c>
       <c r="L3" t="n">
-        <v>48258281150.98</v>
+        <v>42366304737.07</v>
       </c>
       <c r="M3" t="n">
-        <v>19735794910.8</v>
+        <v>19944405204.11</v>
       </c>
       <c r="N3" t="n">
-        <v>7937290283.8</v>
+        <v>8766305136.9</v>
       </c>
       <c r="O3" t="n">
-        <v>11798504627</v>
+        <v>11178100067.21</v>
       </c>
       <c r="P3" t="n">
-        <v>1836141587.57</v>
+        <v>1240853249.15</v>
       </c>
       <c r="Q3" t="n">
         <v>6001785596.99</v>
@@ -2032,180 +2020,170 @@
       <c r="S3" t="n">
         <v>2790208174</v>
       </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
-        <v>57015590672.48</v>
+        <v>51767579598.33</v>
       </c>
       <c r="V3" t="n">
-        <v>39562561604.36</v>
+        <v>34445631517.63</v>
       </c>
       <c r="W3" t="inlineStr"/>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>1934466589.48</v>
+        <v>2126989927.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>58324199.38</v>
+        <v>61219368.54</v>
       </c>
       <c r="AA3" t="n">
-        <v>140621401.07</v>
+        <v>340886533.68</v>
       </c>
       <c r="AB3" t="n">
-        <v>37429149414.43</v>
+        <v>31916535688.11</v>
       </c>
       <c r="AC3" t="n">
-        <v>969372890.45</v>
+        <v>728331018.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>36459776523.98</v>
+        <v>31188204669.86</v>
       </c>
       <c r="AE3" t="n">
-        <v>17453029068.12</v>
+        <v>17321948080.7</v>
       </c>
       <c r="AF3" t="n">
-        <v>731892728.37</v>
+        <v>30693215.71</v>
       </c>
       <c r="AG3" t="n">
-        <v>11769843600.65</v>
+        <v>11984586149.13</v>
       </c>
       <c r="AH3" t="n">
-        <v>6373744656.75</v>
+        <v>6791485849.14</v>
       </c>
       <c r="AI3" t="n">
-        <v>4560896847.23</v>
+        <v>4939959245.87</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1057165472.72</v>
+        <v>1159806396.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>36129493.1</v>
+        <v>111154051.7</v>
       </c>
       <c r="AL3" t="n">
-        <v>182152512.2</v>
+        <v>191742022.38</v>
       </c>
       <c r="AM3" t="n">
-        <v>3285449369.21</v>
+        <v>3477256775.59</v>
       </c>
       <c r="AN3" t="n">
-        <v>76751385583.28</v>
+        <v>71711984802.44</v>
       </c>
       <c r="AO3" t="n">
-        <v>65723221869.9</v>
+        <v>59963463465.7</v>
       </c>
       <c r="AP3" t="n">
-        <v>2721912885.24</v>
+        <v>1611009075.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>303106168.93</v>
-      </c>
-      <c r="AR3" t="inlineStr"/>
+        <v>215599147.09</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>282808172.14</v>
+      </c>
       <c r="AS3" t="n">
-        <v>334535783.49</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
+        <v>281527876.98</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="n">
-        <v>334535783.49</v>
+        <v>281527876.98</v>
       </c>
       <c r="AV3" t="n">
-        <v>1185083287.35</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
+        <v>993460052.58</v>
+      </c>
+      <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="n">
-        <v>1746984884.46</v>
+        <v>945827741.77</v>
       </c>
       <c r="AY3" t="n">
-        <v>1742363232.18</v>
+        <v>941206089.49</v>
       </c>
       <c r="AZ3" t="n">
         <v>4621652.28</v>
       </c>
       <c r="BA3" t="n">
-        <v>59211498622.58</v>
+        <v>55497898967.74</v>
       </c>
       <c r="BB3" t="n">
-        <v>-24677930077.07</v>
+        <v>-21357448546.71</v>
       </c>
       <c r="BC3" t="n">
-        <v>83889428699.64999</v>
+        <v>76855347514.45</v>
       </c>
       <c r="BD3" t="n">
-        <v>5992940288.83</v>
+        <v>4200334056.42</v>
       </c>
       <c r="BE3" t="n">
-        <v>1602620870.78</v>
+        <v>1531170649.11</v>
       </c>
       <c r="BF3" t="n">
-        <v>68153840539.78</v>
+        <v>63434604884.86</v>
       </c>
       <c r="BG3" t="n">
-        <v>8140027000.26</v>
+        <v>7689237924.06</v>
       </c>
       <c r="BH3" t="n">
-        <v>11028163713.38</v>
+        <v>11748521336.74</v>
       </c>
       <c r="BI3" t="n">
-        <v>895043977.4299999</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0</v>
-      </c>
+        <v>1006582623.55</v>
+      </c>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
       <c r="BL3" t="n">
-        <v>255951809.87</v>
+        <v>176111852.8</v>
       </c>
       <c r="BM3" t="n">
-        <v>141150921.85</v>
+        <v>266441119.83</v>
       </c>
       <c r="BN3" t="n">
         <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>3408310.79</v>
+        <v>7926689.34</v>
       </c>
       <c r="BP3" t="n">
-        <v>137742611.06</v>
+        <v>258514430.49</v>
       </c>
       <c r="BQ3" t="n">
-        <v>225444038.96</v>
+        <v>281782462</v>
       </c>
       <c r="BR3" t="n">
-        <v>8410067658.38</v>
+        <v>8668217948.17</v>
       </c>
       <c r="BS3" t="n">
-        <v>-150394370.14</v>
+        <v>-90896704.63</v>
       </c>
       <c r="BT3" t="n">
-        <v>8560462028.52</v>
+        <v>8759114652.799999</v>
       </c>
       <c r="BU3" t="n">
-        <v>1100505306.89</v>
+        <v>1349385330.39</v>
       </c>
       <c r="BV3" t="n">
         <v>1000000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1099505306.89</v>
+        <v>1348385330.39</v>
       </c>
       <c r="BX3" t="n">
-        <v>60769251.65</v>
+        <v>90327169.59</v>
       </c>
       <c r="BY3" t="n">
-        <v>1038736055.24</v>
+        <v>1258058160.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>2790208174</v>
@@ -2214,43 +2192,43 @@
         <v>2790208174</v>
       </c>
       <c r="D4" t="n">
-        <v>36631305188.61</v>
+        <v>41734015873.84</v>
       </c>
       <c r="E4" t="n">
-        <v>43901121837.24</v>
+        <v>49198993015.08</v>
       </c>
       <c r="F4" t="n">
-        <v>10232272325.44</v>
+        <v>10051519742.54</v>
       </c>
       <c r="G4" t="n">
-        <v>49157790586.21</v>
+        <v>54632025807.73</v>
       </c>
       <c r="H4" t="n">
-        <v>-5573426743.96</v>
+        <v>-6424865354.74</v>
       </c>
       <c r="I4" t="n">
-        <v>10232272325.44</v>
+        <v>10051519742.54</v>
       </c>
       <c r="J4" t="n">
-        <v>728331018.25</v>
+        <v>969372890.45</v>
       </c>
       <c r="K4" t="n">
-        <v>11178100067.21</v>
+        <v>11798504627</v>
       </c>
       <c r="L4" t="n">
-        <v>42366304737.07</v>
+        <v>48258281150.98</v>
       </c>
       <c r="M4" t="n">
-        <v>19944405204.11</v>
+        <v>19735794910.8</v>
       </c>
       <c r="N4" t="n">
-        <v>8766305136.9</v>
+        <v>7937290283.8</v>
       </c>
       <c r="O4" t="n">
-        <v>11178100067.21</v>
+        <v>11798504627</v>
       </c>
       <c r="P4" t="n">
-        <v>1240853249.15</v>
+        <v>1836141587.57</v>
       </c>
       <c r="Q4" t="n">
         <v>6001785596.99</v>
@@ -2261,382 +2239,404 @@
       <c r="S4" t="n">
         <v>2790208174</v>
       </c>
-      <c r="T4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
       <c r="U4" t="n">
-        <v>51767579598.33</v>
+        <v>57015590672.48</v>
       </c>
       <c r="V4" t="n">
-        <v>34445631517.63</v>
+        <v>39562561604.36</v>
       </c>
       <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
       <c r="Y4" t="n">
-        <v>2126989927.3</v>
+        <v>1934466589.48</v>
       </c>
       <c r="Z4" t="n">
-        <v>61219368.54</v>
+        <v>58324199.38</v>
       </c>
       <c r="AA4" t="n">
-        <v>340886533.68</v>
+        <v>140621401.07</v>
       </c>
       <c r="AB4" t="n">
-        <v>31916535688.11</v>
+        <v>37429149414.43</v>
       </c>
       <c r="AC4" t="n">
-        <v>728331018.25</v>
+        <v>969372890.45</v>
       </c>
       <c r="AD4" t="n">
-        <v>31188204669.86</v>
+        <v>36459776523.98</v>
       </c>
       <c r="AE4" t="n">
-        <v>17321948080.7</v>
+        <v>17453029068.12</v>
       </c>
       <c r="AF4" t="n">
-        <v>30693215.71</v>
+        <v>731892728.37</v>
       </c>
       <c r="AG4" t="n">
-        <v>11984586149.13</v>
+        <v>11769843600.65</v>
       </c>
       <c r="AH4" t="n">
-        <v>6791485849.14</v>
+        <v>6373744656.75</v>
       </c>
       <c r="AI4" t="n">
-        <v>4939959245.87</v>
+        <v>4560896847.23</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1159806396.2</v>
+        <v>1057165472.72</v>
       </c>
       <c r="AK4" t="n">
-        <v>111154051.7</v>
+        <v>36129493.1</v>
       </c>
       <c r="AL4" t="n">
-        <v>191742022.38</v>
+        <v>182152512.2</v>
       </c>
       <c r="AM4" t="n">
-        <v>3477256775.59</v>
+        <v>3285449369.21</v>
       </c>
       <c r="AN4" t="n">
-        <v>71711984802.44</v>
+        <v>76751385583.28</v>
       </c>
       <c r="AO4" t="n">
-        <v>59963463465.7</v>
+        <v>65723221869.9</v>
       </c>
       <c r="AP4" t="n">
-        <v>1611009075.4</v>
+        <v>2721912885.24</v>
       </c>
       <c r="AQ4" t="n">
-        <v>215599147.09</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>282808172.14</v>
-      </c>
+        <v>303106168.93</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>281527876.98</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
+        <v>334535783.49</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
       <c r="AU4" t="n">
-        <v>281527876.98</v>
+        <v>334535783.49</v>
       </c>
       <c r="AV4" t="n">
-        <v>993460052.58</v>
-      </c>
-      <c r="AW4" t="inlineStr"/>
+        <v>1185083287.35</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
       <c r="AX4" t="n">
-        <v>945827741.77</v>
+        <v>1746984884.46</v>
       </c>
       <c r="AY4" t="n">
-        <v>941206089.49</v>
+        <v>1742363232.18</v>
       </c>
       <c r="AZ4" t="n">
         <v>4621652.28</v>
       </c>
       <c r="BA4" t="n">
-        <v>55497898967.74</v>
+        <v>59211498622.58</v>
       </c>
       <c r="BB4" t="n">
-        <v>-21357448546.71</v>
+        <v>-24677930077.07</v>
       </c>
       <c r="BC4" t="n">
-        <v>76855347514.45</v>
+        <v>83889428699.64999</v>
       </c>
       <c r="BD4" t="n">
-        <v>4200334056.42</v>
+        <v>5992940288.83</v>
       </c>
       <c r="BE4" t="n">
-        <v>1531170649.11</v>
+        <v>1602620870.78</v>
       </c>
       <c r="BF4" t="n">
-        <v>63434604884.86</v>
+        <v>68153840539.78</v>
       </c>
       <c r="BG4" t="n">
-        <v>7689237924.06</v>
+        <v>8140027000.26</v>
       </c>
       <c r="BH4" t="n">
-        <v>11748521336.74</v>
+        <v>11028163713.38</v>
       </c>
       <c r="BI4" t="n">
-        <v>1006582623.55</v>
-      </c>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="inlineStr"/>
+        <v>895043977.4299999</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0</v>
+      </c>
       <c r="BL4" t="n">
-        <v>176111852.8</v>
+        <v>255951809.87</v>
       </c>
       <c r="BM4" t="n">
-        <v>266441119.83</v>
+        <v>141150921.85</v>
       </c>
       <c r="BN4" t="n">
         <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>7926689.34</v>
+        <v>3408310.79</v>
       </c>
       <c r="BP4" t="n">
-        <v>258514430.49</v>
+        <v>137742611.06</v>
       </c>
       <c r="BQ4" t="n">
-        <v>281782462</v>
+        <v>225444038.96</v>
       </c>
       <c r="BR4" t="n">
-        <v>8668217948.17</v>
+        <v>8410067658.38</v>
       </c>
       <c r="BS4" t="n">
-        <v>-90896704.63</v>
+        <v>-150394370.14</v>
       </c>
       <c r="BT4" t="n">
-        <v>8759114652.799999</v>
+        <v>8560462028.52</v>
       </c>
       <c r="BU4" t="n">
-        <v>1349385330.39</v>
+        <v>1100505306.89</v>
       </c>
       <c r="BV4" t="n">
         <v>1000000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1348385330.39</v>
+        <v>1099505306.89</v>
       </c>
       <c r="BX4" t="n">
-        <v>90327169.59</v>
+        <v>60769251.65</v>
       </c>
       <c r="BY4" t="n">
-        <v>1258058160.8</v>
+        <v>1038736055.24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>2790208174</v>
+        <v>3627270626</v>
       </c>
       <c r="C5" t="n">
-        <v>2790208174</v>
+        <v>3627270626</v>
       </c>
       <c r="D5" t="n">
-        <v>35916222552.6</v>
+        <v>36149213931.89</v>
       </c>
       <c r="E5" t="n">
-        <v>40752715786.25</v>
+        <v>49606474965.75</v>
       </c>
       <c r="F5" t="n">
-        <v>9597008989.98</v>
+        <v>14908207053.77</v>
       </c>
       <c r="G5" t="n">
-        <v>47354072702.47</v>
+        <v>53766121201.29</v>
       </c>
       <c r="H5" t="n">
-        <v>-9479411357.969999</v>
+        <v>-10726920109.76</v>
       </c>
       <c r="I5" t="n">
-        <v>9597008989.98</v>
+        <v>14908207053.77</v>
       </c>
       <c r="J5" t="n">
-        <v>692135458.46</v>
+        <v>1161418979.06</v>
       </c>
       <c r="K5" t="n">
-        <v>10506014995.17</v>
+        <v>16757287629.58</v>
       </c>
       <c r="L5" t="n">
-        <v>36816354641.09</v>
+        <v>47545721368.29</v>
       </c>
       <c r="M5" t="n">
-        <v>14353561483.5</v>
+        <v>24899870613.77</v>
       </c>
       <c r="N5" t="n">
-        <v>3847546488.33</v>
+        <v>8142582984.19</v>
       </c>
       <c r="O5" t="n">
-        <v>10506014995.17</v>
+        <v>16757287629.58</v>
       </c>
       <c r="P5" t="n">
-        <v>563525276.85</v>
+        <v>2539210152.78</v>
       </c>
       <c r="Q5" t="n">
-        <v>6017730560.46</v>
+        <v>9349565210.540001</v>
       </c>
       <c r="R5" t="n">
-        <v>2790208174</v>
+        <v>3627270626</v>
       </c>
       <c r="S5" t="n">
-        <v>2790208174</v>
-      </c>
-      <c r="T5" t="inlineStr"/>
+        <v>3627270626</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
       <c r="U5" t="n">
-        <v>52471737956.36</v>
+        <v>58063902576.59</v>
       </c>
       <c r="V5" t="n">
-        <v>31048997489.06</v>
-      </c>
-      <c r="W5" t="n">
-        <v>3803400535.26</v>
-      </c>
-      <c r="X5" t="inlineStr"/>
+        <v>34732184834.21</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
       <c r="Y5" t="n">
-        <v>3810558289.06</v>
+        <v>2537752669.87</v>
       </c>
       <c r="Z5" t="n">
-        <v>68756218.73999999</v>
+        <v>118582311.06</v>
       </c>
       <c r="AA5" t="n">
-        <v>167207876.88</v>
+        <v>125997135.51</v>
       </c>
       <c r="AB5" t="n">
-        <v>27002475104.38</v>
+        <v>31949852717.77</v>
       </c>
       <c r="AC5" t="n">
-        <v>692135458.46</v>
+        <v>1161418979.06</v>
       </c>
       <c r="AD5" t="n">
-        <v>26310339645.92</v>
+        <v>30788433738.71</v>
       </c>
       <c r="AE5" t="n">
-        <v>21422740467.3</v>
+        <v>23331717742.38</v>
       </c>
       <c r="AF5" t="n">
-        <v>3058384259.31</v>
+        <v>647545583.63</v>
       </c>
       <c r="AG5" t="n">
-        <v>13750240681.87</v>
+        <v>17656622247.98</v>
       </c>
       <c r="AH5" t="n">
-        <v>10537718061.38</v>
+        <v>6220399833</v>
       </c>
       <c r="AI5" t="n">
-        <v>4252389016.34</v>
+        <v>4603158100.31</v>
       </c>
       <c r="AJ5" t="n">
-        <v>822903238.91</v>
+        <v>865819195.53</v>
       </c>
       <c r="AK5" t="n">
-        <v>137678575.79</v>
+        <v>40206489.88</v>
       </c>
       <c r="AL5" t="n">
-        <v>162204778.06</v>
+        <v>173252662.91</v>
       </c>
       <c r="AM5" t="n">
-        <v>3129602423.58</v>
+        <v>3523879751.99</v>
       </c>
       <c r="AN5" t="n">
-        <v>66825299439.86</v>
+        <v>82963773190.36</v>
       </c>
       <c r="AO5" t="n">
-        <v>54881970330.53</v>
+        <v>70358975557.74001</v>
       </c>
       <c r="AP5" t="n">
-        <v>1526367011.27</v>
+        <v>3275452363.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13156353.18</v>
+        <v>394538026.16</v>
       </c>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>208447230.71</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
+        <v>335651617.88</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
       <c r="AU5" t="n">
-        <v>208447230.71</v>
+        <v>335651617.88</v>
       </c>
       <c r="AV5" t="n">
-        <v>634098603.72</v>
-      </c>
-      <c r="AW5" t="inlineStr"/>
+        <v>1220158426.68</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
       <c r="AX5" t="n">
-        <v>909006005.1900001</v>
+        <v>1849080575.81</v>
       </c>
       <c r="AY5" t="n">
-        <v>854614286.23</v>
+        <v>1844458923.53</v>
       </c>
       <c r="AZ5" t="n">
-        <v>54391718.96</v>
+        <v>4621652.28</v>
       </c>
       <c r="BA5" t="n">
-        <v>51374407101.26</v>
+        <v>63039997301.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>-18148593744.7</v>
+        <v>-28359527107.42</v>
       </c>
       <c r="BC5" t="n">
-        <v>69523000845.96001</v>
+        <v>91399524408.82001</v>
       </c>
       <c r="BD5" t="n">
-        <v>5906608730.28</v>
+        <v>7336977099.32</v>
       </c>
       <c r="BE5" t="n">
-        <v>1603881533.92</v>
+        <v>1917160993.08</v>
       </c>
       <c r="BF5" t="n">
-        <v>54675512670.24</v>
+        <v>73105399280.73</v>
       </c>
       <c r="BG5" t="n">
-        <v>7336997911.52</v>
+        <v>9039987035.690001</v>
       </c>
       <c r="BH5" t="n">
-        <v>11943329109.33</v>
+        <v>12604797632.62</v>
       </c>
       <c r="BI5" t="n">
-        <v>965594662.83</v>
-      </c>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
+        <v>653199955.25</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
       <c r="BL5" t="n">
-        <v>942834940.1900001</v>
+        <v>230688825.24</v>
       </c>
       <c r="BM5" t="n">
-        <v>411176363.58</v>
+        <v>305356902.25</v>
       </c>
       <c r="BN5" t="n">
         <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>6222614.11</v>
+        <v>13255197.78</v>
       </c>
       <c r="BP5" t="n">
-        <v>404953749.47</v>
+        <v>292101704.47</v>
       </c>
       <c r="BQ5" t="n">
-        <v>337772104.34</v>
+        <v>378576738.21</v>
       </c>
       <c r="BR5" t="n">
-        <v>8354115883.69</v>
+        <v>10176355571.85</v>
       </c>
       <c r="BS5" t="n">
-        <v>-38890442.3</v>
+        <v>-215666184.85</v>
       </c>
       <c r="BT5" t="n">
-        <v>8393006325.99</v>
+        <v>10392021756.7</v>
       </c>
       <c r="BU5" t="n">
-        <v>931835154.7</v>
-      </c>
-      <c r="BV5" t="inlineStr"/>
+        <v>860619639.8200001</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000000</v>
+      </c>
       <c r="BW5" t="n">
-        <v>931835154.7</v>
+        <v>859619639.8200001</v>
       </c>
       <c r="BX5" t="n">
-        <v>55026279.87</v>
+        <v>45055290</v>
       </c>
       <c r="BY5" t="n">
-        <v>876808874.83</v>
+        <v>814564349.8200001</v>
       </c>
     </row>
   </sheetData>
@@ -2892,574 +2892,574 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-1418686398.35</v>
+        <v>-3639774239.44</v>
       </c>
       <c r="C2" t="n">
-        <v>-27315960086.26</v>
+        <v>-31200037900.22</v>
       </c>
       <c r="D2" t="n">
-        <v>27724219245.37</v>
+        <v>35033592969.55</v>
       </c>
       <c r="E2" t="n">
-        <v>-6893111830.92</v>
+        <v>-7076936128.2</v>
       </c>
       <c r="F2" t="n">
-        <v>814564349.8200001</v>
+        <v>876808874.83</v>
       </c>
       <c r="G2" t="n">
-        <v>1038736055.24</v>
+        <v>458962758.93</v>
       </c>
       <c r="H2" t="n">
-        <v>-224171705.42</v>
+        <v>417846115.9</v>
       </c>
       <c r="I2" t="n">
-        <v>1241512200.18</v>
+        <v>4197344477.08</v>
       </c>
       <c r="J2" t="n">
-        <v>2983823312.11</v>
+        <v>2258645697.9</v>
       </c>
       <c r="K2" t="n">
-        <v>-1673893677.32</v>
+        <v>-1529792227.87</v>
       </c>
       <c r="L2" t="n">
-        <v>408259159.11</v>
+        <v>3833555069.33</v>
       </c>
       <c r="M2" t="n">
-        <v>408259159.11</v>
+        <v>3833555069.33</v>
       </c>
       <c r="N2" t="n">
-        <v>-27315960086.26</v>
+        <v>-31200037900.22</v>
       </c>
       <c r="O2" t="n">
-        <v>27724219245.37</v>
+        <v>35033592969.55</v>
       </c>
       <c r="P2" t="n">
-        <v>-6940109338.17</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
+        <v>-7216660249.94</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>4730507.86</v>
+      </c>
       <c r="R2" t="n">
-        <v>-7447900</v>
+        <v>-51628503.81</v>
       </c>
       <c r="S2" t="n">
-        <v>5377100</v>
+        <v>275727117.2</v>
       </c>
       <c r="T2" t="n">
-        <v>-12825000</v>
+        <v>-327355621.01</v>
       </c>
       <c r="U2" t="n">
-        <v>-46758786.81</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
+        <v>-158435094.39</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>-46758786.81</v>
+        <v>-158435094.39</v>
       </c>
       <c r="X2" t="n">
-        <v>-6885902651.36</v>
+        <v>-7011327159.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>7209179.56</v>
+        <v>65608968.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>-6893111830.92</v>
+        <v>-7076936128.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>5474425432.57</v>
+        <v>3437161888.76</v>
       </c>
       <c r="AB2" t="n">
-        <v>-1710843279.53</v>
+        <v>-1985452249.53</v>
       </c>
       <c r="AC2" t="n">
-        <v>-43750233.11</v>
+        <v>12602089.49</v>
       </c>
       <c r="AD2" t="n">
-        <v>602653888.53</v>
+        <v>-74354415.98999999</v>
       </c>
       <c r="AE2" t="n">
-        <v>-160131375.08</v>
+        <v>-121438868.27</v>
       </c>
       <c r="AF2" t="n">
-        <v>-2109615559.87</v>
+        <v>-1802261054.76</v>
       </c>
       <c r="AG2" t="n">
-        <v>1486057359.55</v>
+        <v>1661689788.86</v>
       </c>
       <c r="AH2" t="n">
-        <v>3860070719.05</v>
+        <v>2830698657.45</v>
       </c>
       <c r="AI2" t="n">
-        <v>110415651.01</v>
+        <v>49102750.88</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3749655068.04</v>
+        <v>2781595906.57</v>
       </c>
       <c r="AK2" t="n">
-        <v>-27627239.33</v>
+        <v>-22329941.66</v>
       </c>
       <c r="AL2" t="n">
-        <v>85006.45</v>
+        <v>-13134932.13</v>
       </c>
       <c r="AM2" t="n">
-        <v>1687059000.42</v>
+        <v>858674718.0700001</v>
       </c>
       <c r="AN2" t="n">
-        <v>5474425432.57</v>
+        <v>3437161888.76</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1069768148.49</v>
+        <v>-540556877.12</v>
       </c>
       <c r="AP2" t="n">
-        <v>-7640668331.63</v>
+        <v>-8850928904.540001</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-504558916.95</v>
+        <v>-342166476.11</v>
       </c>
       <c r="AR2" t="n">
-        <v>-1423851089.68</v>
+        <v>-1176722343.84</v>
       </c>
       <c r="AS2" t="n">
-        <v>-5712258325</v>
+        <v>-7332040084.59</v>
       </c>
       <c r="AT2" t="n">
-        <v>14184861912.69</v>
+        <v>12828647670.42</v>
       </c>
       <c r="AU2" t="n">
-        <v>471350927.37</v>
+        <v>92438019.14</v>
       </c>
       <c r="AV2" t="n">
-        <v>13713510985.32</v>
+        <v>12736209651.28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-1340215768.55</v>
+        <v>636239778.37</v>
       </c>
       <c r="C3" t="n">
-        <v>-28355961952.61</v>
+        <v>-37489765511.88</v>
       </c>
       <c r="D3" t="n">
-        <v>32349615871.82</v>
+        <v>37939876731.2</v>
       </c>
       <c r="E3" t="n">
-        <v>-6785419248.65</v>
+        <v>-6692133089.22</v>
       </c>
       <c r="F3" t="n">
-        <v>1038736055.24</v>
+        <v>1134901784.46</v>
       </c>
       <c r="G3" t="n">
-        <v>1134901784.46</v>
+        <v>876808874.83</v>
       </c>
       <c r="H3" t="n">
-        <v>-96165729.22</v>
+        <v>258092909.63</v>
       </c>
       <c r="I3" t="n">
-        <v>268263687.9</v>
+        <v>168237698.92</v>
       </c>
       <c r="J3" t="n">
-        <v>-1357949887.18</v>
+        <v>1693634832.12</v>
       </c>
       <c r="K3" t="n">
-        <v>-1413159377.99</v>
+        <v>-1807460580.67</v>
       </c>
       <c r="L3" t="n">
-        <v>3993653919.21</v>
+        <v>450111219.32</v>
       </c>
       <c r="M3" t="n">
-        <v>3993653919.21</v>
+        <v>450111219.32</v>
       </c>
       <c r="N3" t="n">
-        <v>-28355961952.61</v>
+        <v>-37489765511.88</v>
       </c>
       <c r="O3" t="n">
-        <v>32349615871.82</v>
+        <v>37939876731.2</v>
       </c>
       <c r="P3" t="n">
-        <v>-5809632897.22</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1670003027.72</v>
-      </c>
+        <v>-7238517656.88</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>-189828819</v>
-      </c>
-      <c r="S3" t="n">
-        <v>630525</v>
-      </c>
+        <v>-495773602.7</v>
+      </c>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>-190459344</v>
+        <v>-495773602.7</v>
       </c>
       <c r="U3" t="n">
-        <v>-535414667.43</v>
+        <v>-52137555</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>-535414667.43</v>
+        <v>-52137555</v>
       </c>
       <c r="X3" t="n">
-        <v>-6754392438.51</v>
+        <v>-6690606499.18</v>
       </c>
       <c r="Y3" t="n">
-        <v>31026810.14</v>
+        <v>1526590.04</v>
       </c>
       <c r="Z3" t="n">
-        <v>-6785419248.65</v>
+        <v>-6692133089.22</v>
       </c>
       <c r="AA3" t="n">
-        <v>5445203480.1</v>
+        <v>7328372867.59</v>
       </c>
       <c r="AB3" t="n">
-        <v>-1266008621.33</v>
+        <v>905600434.98</v>
       </c>
       <c r="AC3" t="n">
-        <v>-8454084.949999999</v>
+        <v>-22375019.45</v>
       </c>
       <c r="AD3" t="n">
-        <v>-2569414626.74</v>
+        <v>268213086.71</v>
       </c>
       <c r="AE3" t="n">
-        <v>125290197.98</v>
+        <v>144735243.75</v>
       </c>
       <c r="AF3" t="n">
-        <v>1186569892.38</v>
+        <v>515027123.97</v>
       </c>
       <c r="AG3" t="n">
-        <v>1518685168.76</v>
+        <v>1859590108.53</v>
       </c>
       <c r="AH3" t="n">
-        <v>3528599463.68</v>
+        <v>3339810397.12</v>
       </c>
       <c r="AI3" t="n">
-        <v>61552290.48</v>
+        <v>52299935.96</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3467047173.2</v>
+        <v>3287510461.16</v>
       </c>
       <c r="AK3" t="n">
-        <v>-65691410.83</v>
+        <v>-82734448.86</v>
       </c>
       <c r="AL3" t="n">
-        <v>30334133.67</v>
+        <v>6947800.38</v>
       </c>
       <c r="AM3" t="n">
-        <v>1563160960.68</v>
+        <v>1183712551.32</v>
       </c>
       <c r="AN3" t="n">
-        <v>5445203480.1</v>
+        <v>7328372867.59</v>
       </c>
       <c r="AO3" t="n">
-        <v>-950291775.8</v>
+        <v>42123519.61</v>
       </c>
       <c r="AP3" t="n">
-        <v>-8716332649.809999</v>
+        <v>-9154123360.610001</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-427990260.24</v>
+        <v>-467368309.7</v>
       </c>
       <c r="AR3" t="n">
-        <v>-1441235510.93</v>
+        <v>-1376271639.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>-6847106878.64</v>
+        <v>-7310483411.51</v>
       </c>
       <c r="AT3" t="n">
-        <v>15111827905.71</v>
+        <v>16440372708.59</v>
       </c>
       <c r="AU3" t="n">
-        <v>533995558.43</v>
+        <v>251969084.44</v>
       </c>
       <c r="AV3" t="n">
-        <v>14577832347.28</v>
+        <v>16188403624.15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>636239778.37</v>
+        <v>-1340215768.55</v>
       </c>
       <c r="C4" t="n">
-        <v>-37489765511.88</v>
+        <v>-28355961952.61</v>
       </c>
       <c r="D4" t="n">
-        <v>37939876731.2</v>
+        <v>32349615871.82</v>
       </c>
       <c r="E4" t="n">
-        <v>-6692133089.22</v>
+        <v>-6785419248.65</v>
       </c>
       <c r="F4" t="n">
+        <v>1038736055.24</v>
+      </c>
+      <c r="G4" t="n">
         <v>1134901784.46</v>
       </c>
-      <c r="G4" t="n">
-        <v>876808874.83</v>
-      </c>
       <c r="H4" t="n">
-        <v>258092909.63</v>
+        <v>-96165729.22</v>
       </c>
       <c r="I4" t="n">
-        <v>168237698.92</v>
+        <v>268263687.9</v>
       </c>
       <c r="J4" t="n">
-        <v>1693634832.12</v>
+        <v>-1357949887.18</v>
       </c>
       <c r="K4" t="n">
-        <v>-1807460580.67</v>
+        <v>-1413159377.99</v>
       </c>
       <c r="L4" t="n">
-        <v>450111219.32</v>
+        <v>3993653919.21</v>
       </c>
       <c r="M4" t="n">
-        <v>450111219.32</v>
+        <v>3993653919.21</v>
       </c>
       <c r="N4" t="n">
-        <v>-37489765511.88</v>
+        <v>-28355961952.61</v>
       </c>
       <c r="O4" t="n">
-        <v>37939876731.2</v>
+        <v>32349615871.82</v>
       </c>
       <c r="P4" t="n">
-        <v>-7238517656.88</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+        <v>-5809632897.22</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1670003027.72</v>
+      </c>
       <c r="R4" t="n">
-        <v>-495773602.7</v>
-      </c>
-      <c r="S4" t="inlineStr"/>
+        <v>-189828819</v>
+      </c>
+      <c r="S4" t="n">
+        <v>630525</v>
+      </c>
       <c r="T4" t="n">
-        <v>-495773602.7</v>
+        <v>-190459344</v>
       </c>
       <c r="U4" t="n">
-        <v>-52137555</v>
+        <v>-535414667.43</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>-52137555</v>
+        <v>-535414667.43</v>
       </c>
       <c r="X4" t="n">
-        <v>-6690606499.18</v>
+        <v>-6754392438.51</v>
       </c>
       <c r="Y4" t="n">
-        <v>1526590.04</v>
+        <v>31026810.14</v>
       </c>
       <c r="Z4" t="n">
-        <v>-6692133089.22</v>
+        <v>-6785419248.65</v>
       </c>
       <c r="AA4" t="n">
-        <v>7328372867.59</v>
+        <v>5445203480.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>905600434.98</v>
+        <v>-1266008621.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>-22375019.45</v>
+        <v>-8454084.949999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>268213086.71</v>
+        <v>-2569414626.74</v>
       </c>
       <c r="AE4" t="n">
-        <v>144735243.75</v>
+        <v>125290197.98</v>
       </c>
       <c r="AF4" t="n">
-        <v>515027123.97</v>
+        <v>1186569892.38</v>
       </c>
       <c r="AG4" t="n">
-        <v>1859590108.53</v>
+        <v>1518685168.76</v>
       </c>
       <c r="AH4" t="n">
-        <v>3339810397.12</v>
+        <v>3528599463.68</v>
       </c>
       <c r="AI4" t="n">
-        <v>52299935.96</v>
+        <v>61552290.48</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3287510461.16</v>
+        <v>3467047173.2</v>
       </c>
       <c r="AK4" t="n">
-        <v>-82734448.86</v>
+        <v>-65691410.83</v>
       </c>
       <c r="AL4" t="n">
-        <v>6947800.38</v>
+        <v>30334133.67</v>
       </c>
       <c r="AM4" t="n">
-        <v>1183712551.32</v>
+        <v>1563160960.68</v>
       </c>
       <c r="AN4" t="n">
-        <v>7328372867.59</v>
+        <v>5445203480.1</v>
       </c>
       <c r="AO4" t="n">
-        <v>42123519.61</v>
+        <v>-950291775.8</v>
       </c>
       <c r="AP4" t="n">
-        <v>-9154123360.610001</v>
+        <v>-8716332649.809999</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-467368309.7</v>
+        <v>-427990260.24</v>
       </c>
       <c r="AR4" t="n">
-        <v>-1376271639.4</v>
+        <v>-1441235510.93</v>
       </c>
       <c r="AS4" t="n">
-        <v>-7310483411.51</v>
+        <v>-6847106878.64</v>
       </c>
       <c r="AT4" t="n">
-        <v>16440372708.59</v>
+        <v>15111827905.71</v>
       </c>
       <c r="AU4" t="n">
-        <v>251969084.44</v>
+        <v>533995558.43</v>
       </c>
       <c r="AV4" t="n">
-        <v>16188403624.15</v>
+        <v>14577832347.28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-3639774239.44</v>
+        <v>-1418686398.35</v>
       </c>
       <c r="C5" t="n">
-        <v>-31200037900.22</v>
+        <v>-27315960086.26</v>
       </c>
       <c r="D5" t="n">
-        <v>35033592969.55</v>
+        <v>27724219245.37</v>
       </c>
       <c r="E5" t="n">
-        <v>-7076936128.2</v>
+        <v>-6893111830.92</v>
       </c>
       <c r="F5" t="n">
-        <v>876808874.83</v>
+        <v>814564349.8200001</v>
       </c>
       <c r="G5" t="n">
-        <v>458962758.93</v>
+        <v>1038736055.24</v>
       </c>
       <c r="H5" t="n">
-        <v>417846115.9</v>
+        <v>-224171705.42</v>
       </c>
       <c r="I5" t="n">
-        <v>4197344477.08</v>
+        <v>1241512200.18</v>
       </c>
       <c r="J5" t="n">
-        <v>2258645697.9</v>
+        <v>2983823312.11</v>
       </c>
       <c r="K5" t="n">
-        <v>-1529792227.87</v>
+        <v>-1673893677.32</v>
       </c>
       <c r="L5" t="n">
-        <v>3833555069.33</v>
+        <v>408259159.11</v>
       </c>
       <c r="M5" t="n">
-        <v>3833555069.33</v>
+        <v>408259159.11</v>
       </c>
       <c r="N5" t="n">
-        <v>-31200037900.22</v>
+        <v>-27315960086.26</v>
       </c>
       <c r="O5" t="n">
-        <v>35033592969.55</v>
+        <v>27724219245.37</v>
       </c>
       <c r="P5" t="n">
-        <v>-7216660249.94</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>4730507.86</v>
-      </c>
+        <v>-6940109338.17</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>-51628503.81</v>
+        <v>-7447900</v>
       </c>
       <c r="S5" t="n">
-        <v>275727117.2</v>
+        <v>5377100</v>
       </c>
       <c r="T5" t="n">
-        <v>-327355621.01</v>
+        <v>-12825000</v>
       </c>
       <c r="U5" t="n">
-        <v>-158435094.39</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
+        <v>-46758786.81</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
       <c r="W5" t="n">
-        <v>-158435094.39</v>
+        <v>-46758786.81</v>
       </c>
       <c r="X5" t="n">
-        <v>-7011327159.6</v>
+        <v>-6885902651.36</v>
       </c>
       <c r="Y5" t="n">
-        <v>65608968.6</v>
+        <v>7209179.56</v>
       </c>
       <c r="Z5" t="n">
-        <v>-7076936128.2</v>
+        <v>-6893111830.92</v>
       </c>
       <c r="AA5" t="n">
-        <v>3437161888.76</v>
+        <v>5474425432.57</v>
       </c>
       <c r="AB5" t="n">
-        <v>-1985452249.53</v>
+        <v>-1710843279.53</v>
       </c>
       <c r="AC5" t="n">
-        <v>12602089.49</v>
+        <v>-43750233.11</v>
       </c>
       <c r="AD5" t="n">
-        <v>-74354415.98999999</v>
+        <v>602653888.53</v>
       </c>
       <c r="AE5" t="n">
-        <v>-121438868.27</v>
+        <v>-160131375.08</v>
       </c>
       <c r="AF5" t="n">
-        <v>-1802261054.76</v>
+        <v>-2109615559.87</v>
       </c>
       <c r="AG5" t="n">
-        <v>1661689788.86</v>
+        <v>1486057359.55</v>
       </c>
       <c r="AH5" t="n">
-        <v>2830698657.45</v>
+        <v>3860070719.05</v>
       </c>
       <c r="AI5" t="n">
-        <v>49102750.88</v>
+        <v>110415651.01</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2781595906.57</v>
+        <v>3749655068.04</v>
       </c>
       <c r="AK5" t="n">
-        <v>-22329941.66</v>
+        <v>-27627239.33</v>
       </c>
       <c r="AL5" t="n">
-        <v>-13134932.13</v>
+        <v>85006.45</v>
       </c>
       <c r="AM5" t="n">
-        <v>858674718.0700001</v>
+        <v>1687059000.42</v>
       </c>
       <c r="AN5" t="n">
-        <v>3437161888.76</v>
+        <v>5474425432.57</v>
       </c>
       <c r="AO5" t="n">
-        <v>-540556877.12</v>
+        <v>-1069768148.49</v>
       </c>
       <c r="AP5" t="n">
-        <v>-8850928904.540001</v>
+        <v>-7640668331.63</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-342166476.11</v>
+        <v>-504558916.95</v>
       </c>
       <c r="AR5" t="n">
-        <v>-1176722343.84</v>
+        <v>-1423851089.68</v>
       </c>
       <c r="AS5" t="n">
-        <v>-7332040084.59</v>
+        <v>-5712258325</v>
       </c>
       <c r="AT5" t="n">
-        <v>12828647670.42</v>
+        <v>14184861912.69</v>
       </c>
       <c r="AU5" t="n">
-        <v>92438019.14</v>
+        <v>471350927.37</v>
       </c>
       <c r="AV5" t="n">
-        <v>12736209651.28</v>
+        <v>13713510985.32</v>
       </c>
     </row>
   </sheetData>
@@ -4044,207 +4044,207 @@
       </c>
       <c r="DJ1" t="inlineStr">
         <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>epsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>prevName</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>nameChangeDate</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>epsCurrentYear</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>prevName</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>nameChangeDate</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="EQ1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="ER1" t="inlineStr">
+      <c r="ET1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="ES1" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="ET1" t="inlineStr">
+      <c r="EV1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="EU1" t="inlineStr">
+      <c r="EW1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="EV1" t="inlineStr">
+      <c r="EX1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EW1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EX1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="EY1" t="inlineStr">
@@ -4344,79 +4344,79 @@
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>6.96</v>
+        <v>5.46</v>
       </c>
       <c r="U2" t="n">
-        <v>6.26</v>
+        <v>5.85</v>
       </c>
       <c r="V2" t="n">
-        <v>6.94</v>
+        <v>5.2</v>
       </c>
       <c r="W2" t="n">
-        <v>7.25</v>
+        <v>5.53</v>
       </c>
       <c r="X2" t="n">
-        <v>6.96</v>
+        <v>5.46</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.26</v>
+        <v>5.85</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.94</v>
+        <v>5.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.25</v>
+        <v>5.53</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.79</v>
+        <v>1.32</v>
       </c>
       <c r="AD2" t="n">
-        <v>1764028800</v>
+        <v>1780963200</v>
       </c>
       <c r="AE2" t="n">
         <v>1.14</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.732</v>
+        <v>0.73</v>
       </c>
       <c r="AG2" t="n">
-        <v>143.59999</v>
+        <v>110.4</v>
       </c>
       <c r="AH2" t="n">
-        <v>47.866665</v>
+        <v>36.8</v>
       </c>
       <c r="AI2" t="n">
-        <v>139936981</v>
+        <v>84191654</v>
       </c>
       <c r="AJ2" t="n">
-        <v>139936981</v>
+        <v>84191654</v>
       </c>
       <c r="AK2" t="n">
-        <v>89733858</v>
+        <v>73107555</v>
       </c>
       <c r="AL2" t="n">
-        <v>91040193</v>
+        <v>58530854</v>
       </c>
       <c r="AM2" t="n">
-        <v>91040193</v>
+        <v>58530854</v>
       </c>
       <c r="AN2" t="n">
-        <v>7.17</v>
+        <v>5.51</v>
       </c>
       <c r="AO2" t="n">
-        <v>7.18</v>
+        <v>5.52</v>
       </c>
       <c r="AP2" t="n">
-        <v>26043803648</v>
+        <v>20022534144</v>
       </c>
       <c r="AQ2" t="n">
-        <v>26043803094</v>
+        <v>19804897617</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.97</v>
+        <v>4.98</v>
       </c>
       <c r="AS2" t="n">
         <v>8.369999999999999</v>
@@ -4428,19 +4428,19 @@
         <v>1.846153</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.023689</v>
+        <v>1.5558167</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.6912</v>
+        <v>6.5626</v>
       </c>
       <c r="AX2" t="n">
-        <v>6.3169</v>
+        <v>6.3809</v>
       </c>
       <c r="AY2" t="n">
         <v>0.057</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.008189655000000001</v>
+        <v>0.010439561</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>90193510400</v>
+        <v>84172242944</v>
       </c>
       <c r="BD2" t="n">
         <v>0.01289</v>
@@ -4475,7 +4475,7 @@
         <v>4.845</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.4819402</v>
+        <v>1.139319</v>
       </c>
       <c r="BL2" t="n">
         <v>1767139200</v>
@@ -4507,22 +4507,22 @@
         <v>1153872000</v>
       </c>
       <c r="BU2" t="n">
-        <v>7.008</v>
+        <v>6.54</v>
       </c>
       <c r="BV2" t="n">
-        <v>13.984</v>
+        <v>13.05</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.39147282</v>
+        <v>0.08548712999999999</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.27697718</v>
+        <v>0.24487448</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.021</v>
+        <v>0.016</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1764028800</v>
+        <v>1780963200</v>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="CB2" t="n">
-        <v>7.18</v>
+        <v>5.52</v>
       </c>
       <c r="CC2" t="n">
         <v>7.13</v>
@@ -4647,156 +4647,156 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="DJ2" t="n">
+        <v>1.0989</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>0.059999943</v>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>5.2 - 5.53</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>Shenzhen</t>
+        </is>
+      </c>
+      <c r="DO2" t="n">
+        <v>73107555</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>0.5399999599999999</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>0.10843372</v>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>4.98 - 8.37</t>
+        </is>
+      </c>
+      <c r="DS2" t="n">
+        <v>-2.85</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>-0.3405018</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>8.548712999999999</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>1651229940</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>1651492800</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>39.42857</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>-1.0426002</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>-0.15886998</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>-0.8608999000000001</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>-0.13491826</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>Jilin Electric Power Co.,Ltd.</t>
+        </is>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>SPIC GREEN ENERGY CO LTD</t>
+        </is>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>SPIC Green Energy Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="EL2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="EN2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>1033003800000</v>
+      </c>
+      <c r="EP2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DK2" t="n">
-        <v>1780038252</v>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>SPIC GREEN ENERGY CO LTD</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>SPIC Green Energy Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="DO2" t="b">
+      <c r="EQ2" t="n">
+        <v>1782111897</v>
+      </c>
+      <c r="ER2" t="inlineStr">
+        <is>
+          <t>SHZ</t>
+        </is>
+      </c>
+      <c r="ES2" t="inlineStr">
+        <is>
+          <t>finmb_9735820</t>
+        </is>
+      </c>
+      <c r="ET2" t="inlineStr">
+        <is>
+          <t>Asia/Shanghai</t>
+        </is>
+      </c>
+      <c r="EU2" t="inlineStr">
+        <is>
+          <t>CST</t>
+        </is>
+      </c>
+      <c r="EV2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="EW2" t="inlineStr">
+        <is>
+          <t>cn_market</t>
+        </is>
+      </c>
+      <c r="EX2" t="b">
         <v>0</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>1033003800000</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>0.21999979</v>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>6.94 - 7.25</t>
-        </is>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>Shenzhen</t>
-        </is>
-      </c>
-      <c r="DT2" t="n">
-        <v>89733858</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>0.44466802</v>
-      </c>
-      <c r="DW2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>4.97 - 8.37</t>
-        </is>
-      </c>
-      <c r="DY2" t="n">
-        <v>-1.19</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-0.14217444</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>39.14728</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>1651229940</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>1651492800</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>51.285713</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>0.48880005</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>0.07305118400000001</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>0.86310005</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>0.13663349</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EN2" t="inlineStr">
-        <is>
-          <t>Jilin Electric Power Co.,Ltd.</t>
-        </is>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="EP2" t="inlineStr">
-        <is>
-          <t>SHZ</t>
-        </is>
-      </c>
-      <c r="EQ2" t="inlineStr">
-        <is>
-          <t>finmb_9735820</t>
-        </is>
-      </c>
-      <c r="ER2" t="inlineStr">
-        <is>
-          <t>Asia/Shanghai</t>
-        </is>
-      </c>
-      <c r="ES2" t="inlineStr">
-        <is>
-          <t>CST</t>
-        </is>
-      </c>
-      <c r="ET2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EU2" t="inlineStr">
-        <is>
-          <t>cn_market</t>
-        </is>
-      </c>
-      <c r="EV2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EW2" t="n">
-        <v>3.1609166</v>
-      </c>
-      <c r="EX2" t="n">
-        <v>7.18</v>
       </c>
       <c r="EY2" t="inlineStr"/>
     </row>
